--- a/Results/glm_sensitivity_Peninsula_excel.xlsx
+++ b/Results/glm_sensitivity_Peninsula_excel.xlsx
@@ -1,21 +1,71 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\OneDrive\Desktop\Artigos_coauthor\Iberian_plants\Extinction_dynamics_Iberic\Results\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D228B9-45E8-44B0-92E5-25C9BBCF9E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Corrected age</t>
+  </si>
+  <si>
+    <t>Diversification rates</t>
+  </si>
+  <si>
+    <t>Significant (%)</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>Mean estimate</t>
+  </si>
+  <si>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>Ex. scenario</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -30,6 +80,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,10 +115,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -63,13 +138,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +190,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +224,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +259,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,291 +435,213 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>term</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>mean_estimate</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sd_estimate</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>median_estimate</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>mean_p</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>prop_significant</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>2.993004455840553</v>
-      </c>
-      <c r="D2">
-        <v>0.02390706406869614</v>
-      </c>
-      <c r="E2">
-        <v>2.99163354274307</v>
-      </c>
-      <c r="F2">
-        <v>9.031488320882919E-104</v>
-      </c>
-      <c r="G2">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>3.023590646097744</v>
-      </c>
-      <c r="D3">
-        <v>0.03081250725036918</v>
-      </c>
-      <c r="E3">
-        <v>3.022693824574054</v>
-      </c>
-      <c r="F3">
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5">
+        <v>2.9930044558405529</v>
+      </c>
+      <c r="D2" s="5">
+        <v>2.3907064068696141E-2</v>
+      </c>
+      <c r="E2" s="5">
+        <v>9.0314883208829195E-104</v>
+      </c>
+      <c r="F2" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5">
+        <v>-2.7078789748704781E-3</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1.1644767858692651E-3</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.67787770147384219</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0.16715599975552251</v>
+      </c>
+      <c r="D4" s="5">
+        <v>6.9964450363799086E-2</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.73196434214939632</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3.0235906460977442</v>
+      </c>
+      <c r="D5" s="5">
+        <v>3.081250725036918E-2</v>
+      </c>
+      <c r="E5" s="5">
         <v>6.162570875379071E-67</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>3.092741164348967</v>
-      </c>
-      <c r="D4">
-        <v>0.04117242771649132</v>
-      </c>
-      <c r="E4">
-        <v>3.096619910062677</v>
-      </c>
-      <c r="F4">
+      <c r="F5" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5">
+        <v>-6.5161731326212969E-3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2.5062608208558609E-3</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.62364916977270712</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.11760079031478179</v>
+      </c>
+      <c r="D7" s="5">
+        <v>6.9952904953001008E-2</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.81319236590599109</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3.0927411643489671</v>
+      </c>
+      <c r="D8" s="5">
+        <v>4.1172427716491322E-2</v>
+      </c>
+      <c r="E8" s="5">
         <v>1.033596349810303E-41</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Corrected age</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>-0.002707878974870478</v>
-      </c>
-      <c r="D5">
-        <v>0.001164476785869265</v>
-      </c>
-      <c r="E5">
-        <v>-0.002676552351103071</v>
-      </c>
-      <c r="F5">
-        <v>0.6778777014738422</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Corrected age</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>-0.006516173132621297</v>
-      </c>
-      <c r="D6">
-        <v>0.002506260820855861</v>
-      </c>
-      <c r="E6">
-        <v>-0.006720174919391845</v>
-      </c>
-      <c r="F6">
-        <v>0.6236491697727071</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Corrected age</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>-0.01905175860824179</v>
-      </c>
-      <c r="D7">
-        <v>0.005299026564918281</v>
-      </c>
-      <c r="E7">
-        <v>-0.01929946819217077</v>
-      </c>
-      <c r="F7">
-        <v>0.4963030738728504</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Diversification rates</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>0.1671559997555225</v>
-      </c>
-      <c r="D8">
-        <v>0.06996445036379909</v>
-      </c>
-      <c r="E8">
-        <v>0.1669131449534956</v>
-      </c>
-      <c r="F8">
-        <v>0.7319643421493963</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Diversification rates</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Intermediate</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.1176007903147818</v>
-      </c>
-      <c r="D9">
-        <v>0.06995290495300101</v>
-      </c>
-      <c r="E9">
-        <v>0.1143594077977501</v>
-      </c>
-      <c r="F9">
-        <v>0.8131923659059911</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Diversification rates</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>0.01865414360444746</v>
-      </c>
-      <c r="D10">
-        <v>0.072360523177113</v>
-      </c>
-      <c r="E10">
-        <v>0.01711931069709272</v>
-      </c>
-      <c r="F10">
+      <c r="F8" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-1.9051758608241789E-2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>5.2990265649182806E-3</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.49630307387285039</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1.8654143604447459E-2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>7.2360523177113001E-2</v>
+      </c>
+      <c r="E10" s="5">
         <v>0.9187411838827455</v>
       </c>
-      <c r="G10">
+      <c r="F10" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>